--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/NEW_YORK_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/NEW_YORK_2016.xlsx
@@ -2641,7 +2641,7 @@
         <v>26</v>
       </c>
       <c r="D127">
-        <v>0.0009626420822688733</v>
+        <v>0.0009626420822688732</v>
       </c>
     </row>
     <row r="128">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C230">
@@ -5089,7 +5089,7 @@
         <v>26</v>
       </c>
       <c r="D263">
-        <v>0.0009626420822688733</v>
+        <v>0.0009626420822688732</v>
       </c>
     </row>
     <row r="264">
@@ -5467,7 +5467,7 @@
         <v>261</v>
       </c>
       <c r="D284">
-        <v>0.009663445518160613</v>
+        <v>0.009663445518160611</v>
       </c>
     </row>
     <row r="285">
@@ -9895,7 +9895,7 @@
         <v>27</v>
       </c>
       <c r="D530">
-        <v>0.0009996667777407531</v>
+        <v>0.0009996667777407533</v>
       </c>
     </row>
     <row r="531">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 08-</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C641">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C683">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C684">
@@ -17077,7 +17077,7 @@
         <v>26</v>
       </c>
       <c r="D929">
-        <v>0.0009626420822688733</v>
+        <v>0.0009626420822688732</v>
       </c>
     </row>
     <row r="930">
@@ -17617,7 +17617,7 @@
         <v>26</v>
       </c>
       <c r="D959">
-        <v>0.0009626420822688733</v>
+        <v>0.0009626420822688732</v>
       </c>
     </row>
     <row r="960">
@@ -20706,7 +20706,7 @@
       </c>
       <c r="B1131" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1131">
@@ -22873,7 +22873,7 @@
         <v>27</v>
       </c>
       <c r="D1251">
-        <v>0.0009996667777407531</v>
+        <v>0.0009996667777407533</v>
       </c>
     </row>
     <row r="1252">
